--- a/output/pdf_financials_xlsx/LABS.xlsx
+++ b/output/pdf_financials_xlsx/LABS.xlsx
@@ -3519,22 +3519,22 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.000193</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.003409</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.01696</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.021909</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.028398</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.029532</v>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
@@ -3863,10 +3863,10 @@
         <v>0</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.002282</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>0.000647</v>
       </c>
       <c r="E103" s="3" t="n">
         <v>0</v>
@@ -3956,10 +3956,10 @@
         <v>0.001194</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.008946000000000001</v>
+        <v>-0.011228</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.050395</v>
+        <v>-0.049748</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0.00031</v>
@@ -6410,7 +6410,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>0.000193</v>
       </c>
@@ -7388,7 +7392,11 @@
           <t>Prepaids and deposits 10</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="n">
         <v>0.000418</v>
       </c>
@@ -16064,7 +16072,11 @@
           <t>Change in prepaids and deposits</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LABS.xlsx
+++ b/output/pdf_financials_xlsx/LABS.xlsx
@@ -4148,10 +4148,10 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.000311</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>7e-06</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -14444,7 +14444,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
